--- a/InputData/indst/IFSRF/Industrial Feedstock Switching Recipient Fuel.xlsx
+++ b/InputData/indst/IFSRF/Industrial Feedstock Switching Recipient Fuel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\indst\IFSRF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96EB2BC-0030-40BA-9364-0A5C36AD3468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A002F07-AF76-49E7-90BE-A5BA34F90A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59310" yWindow="1710" windowWidth="21600" windowHeight="12525" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="61260" yWindow="1725" windowWidth="24900" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
   <si>
     <t>RHPF Recipient Hydrogen Pathway Fractions</t>
   </si>
@@ -86,6 +86,12 @@
   </si>
   <si>
     <t>For the U.S. model, it is configured to shift natural gas and coal to</t>
+  </si>
+  <si>
+    <t>green hydrogen if</t>
+  </si>
+  <si>
+    <t>low carbon hydrogen if</t>
   </si>
 </sst>
 </file>
@@ -496,7 +502,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34.26953125" customWidth="1"/>
@@ -504,7 +510,7 @@
     <col min="7" max="8" width="16.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="58" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -538,8 +544,14 @@
       <c r="K1" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
@@ -573,8 +585,14 @@
       <c r="K2" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L2" s="3">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -608,8 +626,14 @@
       <c r="K3" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L3" s="3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -643,8 +667,14 @@
       <c r="K4" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L4" s="3">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -678,8 +708,14 @@
       <c r="K5" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L5" s="3">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -713,8 +749,14 @@
       <c r="K6" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L6" s="3">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -748,8 +790,14 @@
       <c r="K7" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L7" s="3">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -783,8 +831,14 @@
       <c r="K8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -818,8 +872,14 @@
       <c r="K9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -853,8 +913,14 @@
       <c r="K10" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -862,10 +928,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="3">
         <v>0</v>
@@ -886,8 +952,100 @@
         <v>0</v>
       </c>
       <c r="K11" s="3">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
+        <v>1</v>
+      </c>
+      <c r="L12" s="3">
+        <v>1</v>
+      </c>
+      <c r="M12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/indst/IFSRF/Industrial Feedstock Switching Recipient Fuel.xlsx
+++ b/InputData/indst/IFSRF/Industrial Feedstock Switching Recipient Fuel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\indst\IFSRF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A002F07-AF76-49E7-90BE-A5BA34F90A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96EB2BC-0030-40BA-9364-0A5C36AD3468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61260" yWindow="1725" windowWidth="24900" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="59310" yWindow="1710" windowWidth="21600" windowHeight="12525" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
   <si>
     <t>RHPF Recipient Hydrogen Pathway Fractions</t>
   </si>
@@ -86,12 +86,6 @@
   </si>
   <si>
     <t>For the U.S. model, it is configured to shift natural gas and coal to</t>
-  </si>
-  <si>
-    <t>green hydrogen if</t>
-  </si>
-  <si>
-    <t>low carbon hydrogen if</t>
   </si>
 </sst>
 </file>
@@ -502,7 +496,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34.26953125" customWidth="1"/>
@@ -510,7 +504,7 @@
     <col min="7" max="8" width="16.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="58" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -544,14 +538,8 @@
       <c r="K1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
@@ -585,14 +573,8 @@
       <c r="K2" s="3">
         <v>0</v>
       </c>
-      <c r="L2" s="3">
-        <v>0</v>
-      </c>
-      <c r="M2" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -626,14 +608,8 @@
       <c r="K3" s="3">
         <v>0</v>
       </c>
-      <c r="L3" s="3">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -667,14 +643,8 @@
       <c r="K4" s="3">
         <v>0</v>
       </c>
-      <c r="L4" s="3">
-        <v>0</v>
-      </c>
-      <c r="M4" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -708,14 +678,8 @@
       <c r="K5" s="3">
         <v>0</v>
       </c>
-      <c r="L5" s="3">
-        <v>0</v>
-      </c>
-      <c r="M5" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -749,14 +713,8 @@
       <c r="K6" s="3">
         <v>0</v>
       </c>
-      <c r="L6" s="3">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -790,14 +748,8 @@
       <c r="K7" s="3">
         <v>0</v>
       </c>
-      <c r="L7" s="3">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -831,14 +783,8 @@
       <c r="K8" s="3">
         <v>0</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -872,14 +818,8 @@
       <c r="K9" s="3">
         <v>0</v>
       </c>
-      <c r="L9" s="3">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -913,14 +853,8 @@
       <c r="K10" s="3">
         <v>0</v>
       </c>
-      <c r="L10" s="3">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -928,10 +862,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="3">
         <v>0</v>
@@ -952,100 +886,8 @@
         <v>0</v>
       </c>
       <c r="K11" s="3">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3">
-        <v>0</v>
-      </c>
-      <c r="M11" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="3">
-        <v>0</v>
-      </c>
-      <c r="C12" s="3">
-        <v>1</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1</v>
-      </c>
-      <c r="M12" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="3">
-        <v>0</v>
-      </c>
-      <c r="C13" s="3">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3">
-        <v>0</v>
-      </c>
-      <c r="K13" s="3">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3">
-        <v>0</v>
-      </c>
-      <c r="M13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
